--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table29.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table29.xlsx
@@ -542,13 +542,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
